--- a/Model/test/data_example_table.xlsx
+++ b/Model/test/data_example_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/SimpleDocGenerator/Model/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7881BF06-A6F9-D948-9091-4609DAA0DAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3032E5D2-F658-F142-8CF8-F3A2680DDFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4420" yWindow="660" windowWidth="24980" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="121">
   <si>
     <t>Участок</t>
   </si>
@@ -83,15 +83,9 @@
     <t>2</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>СОЭБ-Н/1</t>
   </si>
   <si>
-    <t>602581142</t>
-  </si>
-  <si>
     <t>ВОСХОД УЛ.</t>
   </si>
   <si>
@@ -110,9 +104,6 @@
     <t>ЖЕЛЕЗНОДОРОЖНАЯ УЛ.</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>Б024252</t>
   </si>
   <si>
@@ -399,6 +390,18 @@
   </si>
   <si>
     <t>МКД ул.Мира, д.7, д.Устюжанино</t>
+  </si>
+  <si>
+    <t>0007646079</t>
+  </si>
+  <si>
+    <t>0602581142</t>
+  </si>
+  <si>
+    <t>11/4</t>
+  </si>
+  <si>
+    <t>22/333333</t>
   </si>
 </sst>
 </file>
@@ -491,7 +494,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -515,9 +518,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -534,6 +534,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -898,8 +905,8 @@
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="9" customWidth="1"/>
@@ -918,707 +925,707 @@
     <col min="20" max="16384" width="9.1640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>98</v>
+      <c r="C1" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G1" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>100</v>
+        <v>81</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="11">
-        <v>602581142</v>
-      </c>
-      <c r="D2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="18" t="s">
         <v>16</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>18</v>
       </c>
       <c r="I2" t="s">
         <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>104</v>
+        <v>111</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>101</v>
       </c>
       <c r="O2" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="18" t="s">
-        <v>92</v>
+      <c r="R2" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="19">
+        <v>20246035</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L3" t="s">
+        <v>83</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="N3" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="11">
-        <v>20246035</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>87</v>
-      </c>
-      <c r="L3" t="s">
-        <v>86</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="N3" s="17" t="s">
-        <v>105</v>
-      </c>
       <c r="O3" t="s">
-        <v>15</v>
-      </c>
-      <c r="R3" s="18" t="s">
-        <v>92</v>
+        <v>14</v>
+      </c>
+      <c r="R3" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="19">
+        <v>52011200</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L4" t="s">
+        <v>83</v>
+      </c>
+      <c r="M4" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="11">
-        <v>52011200</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" t="s">
-        <v>87</v>
-      </c>
-      <c r="L4" t="s">
-        <v>86</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="N4" s="17" t="s">
-        <v>106</v>
+      <c r="N4" s="16" t="s">
+        <v>103</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R4" s="18" t="s">
-        <v>92</v>
+        <v>23</v>
+      </c>
+      <c r="R4" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="11">
+        <v>99</v>
+      </c>
+      <c r="C5" s="19">
         <v>10437018</v>
       </c>
       <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="19" t="s">
+      <c r="J5" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" t="s">
-        <v>36</v>
-      </c>
       <c r="K5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="N5" s="17" t="s">
-        <v>107</v>
+        <v>114</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>104</v>
       </c>
       <c r="O5" t="s">
-        <v>35</v>
-      </c>
-      <c r="R5" s="18" t="s">
-        <v>92</v>
+        <v>32</v>
+      </c>
+      <c r="R5" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="11">
+        <v>99</v>
+      </c>
+      <c r="C6" s="19">
         <v>102521002</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>41</v>
+        <v>36</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>38</v>
       </c>
       <c r="I6" t="s">
         <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="N6" s="17" t="s">
-        <v>108</v>
+        <v>112</v>
+      </c>
+      <c r="N6" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="O6" t="s">
         <v>10</v>
       </c>
-      <c r="R6" s="18" t="s">
+      <c r="R6" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="S6" s="8" t="s">
         <v>92</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="11">
+        <v>99</v>
+      </c>
+      <c r="C7" s="19">
         <v>61078056</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
+        <v>48</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="21"/>
+      <c r="H7" s="18"/>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L7" t="s">
+        <v>83</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="O7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P7" t="s">
         <v>86</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="O7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P7" t="s">
+      <c r="R7" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="R7" s="18" t="s">
+      <c r="S7" s="8" t="s">
         <v>92</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="11">
-        <v>7646079</v>
+        <v>74</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="18" t="s">
         <v>4</v>
       </c>
       <c r="I8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>109</v>
+        <v>115</v>
+      </c>
+      <c r="N8" s="16" t="s">
+        <v>106</v>
       </c>
       <c r="O8" t="s">
-        <v>54</v>
-      </c>
-      <c r="R8" s="18" t="s">
-        <v>93</v>
+        <v>51</v>
+      </c>
+      <c r="R8" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C9" s="11">
+        <v>99</v>
+      </c>
+      <c r="C9" s="19">
         <v>10331062</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="19" t="s">
-        <v>50</v>
+      <c r="H9" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>108</v>
+        <v>112</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="O9" t="s">
-        <v>20</v>
-      </c>
-      <c r="R9" s="18" t="s">
-        <v>93</v>
+        <v>18</v>
+      </c>
+      <c r="R9" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S9" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="11">
+        <v>99</v>
+      </c>
+      <c r="C10" s="19">
         <v>10345065</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>57</v>
       </c>
       <c r="I10" t="s">
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>110</v>
+        <v>114</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>107</v>
       </c>
       <c r="O10" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="18" t="s">
-        <v>93</v>
+      <c r="R10" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="11">
+        <v>99</v>
+      </c>
+      <c r="C11" s="19">
         <v>10456029</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>37</v>
+        <v>61</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>34</v>
       </c>
       <c r="I11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>108</v>
+        <v>112</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="O11" t="s">
-        <v>15</v>
-      </c>
-      <c r="R11" s="18" t="s">
-        <v>93</v>
+        <v>14</v>
+      </c>
+      <c r="R11" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="11">
+        <v>59</v>
+      </c>
+      <c r="C12" s="19">
         <v>2637106</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="E12" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="19" t="s">
-        <v>18</v>
+      <c r="H12" s="18" t="s">
+        <v>16</v>
       </c>
       <c r="I12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>111</v>
+        <v>116</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="O12" t="s">
-        <v>38</v>
-      </c>
-      <c r="R12" s="18" t="s">
-        <v>93</v>
+        <v>35</v>
+      </c>
+      <c r="R12" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S12" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="11">
+        <v>99</v>
+      </c>
+      <c r="C13" s="19">
         <v>30421010</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>47</v>
+        <v>65</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>44</v>
       </c>
       <c r="I13" t="s">
         <v>9</v>
       </c>
       <c r="J13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>107</v>
+        <v>114</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>104</v>
       </c>
       <c r="O13" t="s">
         <v>5</v>
       </c>
-      <c r="R13" s="18" t="s">
-        <v>93</v>
+      <c r="R13" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" s="11">
+        <v>110</v>
+      </c>
+      <c r="C14" s="19">
         <v>51932008</v>
       </c>
       <c r="D14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" t="s">
-        <v>73</v>
-      </c>
-      <c r="J14" t="s">
-        <v>74</v>
-      </c>
       <c r="K14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>109</v>
       </c>
       <c r="O14" t="s">
-        <v>73</v>
-      </c>
-      <c r="R14" s="18" t="s">
-        <v>93</v>
+        <v>70</v>
+      </c>
+      <c r="R14" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="S14" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
@@ -1718,7 +1725,7 @@
       <c r="D47" s="2"/>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C48" s="16"/>
+      <c r="C48" s="15"/>
       <c r="D48" s="2"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
@@ -1782,7 +1789,7 @@
       <c r="D68" s="2"/>
     </row>
     <row r="69" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C69" s="16"/>
+      <c r="C69" s="15"/>
       <c r="D69" s="2"/>
     </row>
     <row r="70" spans="3:4" x14ac:dyDescent="0.2">
@@ -1792,18 +1799,18 @@
       <c r="D71" s="2"/>
     </row>
     <row r="72" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C72" s="16"/>
+      <c r="C72" s="15"/>
       <c r="D72" s="2"/>
     </row>
     <row r="73" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C73" s="16"/>
+      <c r="C73" s="15"/>
       <c r="D73" s="2"/>
     </row>
     <row r="74" spans="3:4" x14ac:dyDescent="0.2">
       <c r="D74" s="2"/>
     </row>
     <row r="75" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C75" s="16"/>
+      <c r="C75" s="15"/>
       <c r="D75" s="2"/>
     </row>
     <row r="76" spans="3:4" x14ac:dyDescent="0.2">
@@ -1837,7 +1844,7 @@
       <c r="D85" s="2"/>
     </row>
     <row r="86" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C86" s="16"/>
+      <c r="C86" s="15"/>
       <c r="D86" s="2"/>
     </row>
     <row r="87" spans="3:4" x14ac:dyDescent="0.2">
@@ -1850,7 +1857,7 @@
       <c r="D89" s="2"/>
     </row>
     <row r="90" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C90" s="16"/>
+      <c r="C90" s="15"/>
       <c r="D90" s="2"/>
     </row>
     <row r="91" spans="3:4" x14ac:dyDescent="0.2">
